--- a/scoutlist.xlsx
+++ b/scoutlist.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Teleop List" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Auto List" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="States List" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Score List" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,1870 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Coral L1 (teleop) score</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Coral L2 (teleop) score</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Coral L3 (teleop) score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Coral L4 (teleop) score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Algae in Processor (teleop) score</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Algea in Net (teleop) score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total teleop score score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9.666666666666666</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.583333333333334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.33333333333334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2811</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>30.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4488</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7.222222222222222</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11.88888888888889</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6465</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>20.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9450</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9998</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7.666666666666666</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10.22222222222222</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.777777777777778</v>
+      </c>
+      <c r="H7" t="n">
+        <v>38.99999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.111111111111112</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10.66666666666667</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.199999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>21</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4692</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="E10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>17.11111111111111</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9993</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>21</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9994</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2412</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="n">
+        <v>13</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.875</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>51.125</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2521</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9.285714285714286</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4043</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>14</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6343</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.352941176470588</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12.64705882352941</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15.29411764705882</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9992</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2990</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12.875</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3636</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="C19" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.91666666666667</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="H19" t="n">
+        <v>44.00000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5468</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24</v>
+      </c>
+      <c r="E20" t="n">
+        <v>26.66666666666666</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>58.91666666666666</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6696</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>13.77777777777778</v>
+      </c>
+      <c r="E21" t="n">
+        <v>15</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8.888888888888889</v>
+      </c>
+      <c r="H21" t="n">
+        <v>41.77777777777777</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9997</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2557</v>
+      </c>
+      <c r="B23" t="n">
+        <v>11.71428571428571</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>19.14285714285714</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6443</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9.714285714285714</v>
+      </c>
+      <c r="E24" t="n">
+        <v>13.57142857142857</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>25.28571428571428</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9567</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8.333333333333332</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9995</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Coral L1 (auto) score</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Coral L2 (auto) score</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Coral L3 (auto) score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Coral L4 (auto) score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Algae in Processor (auto) score</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Algea in Net (auto) score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total auto score score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7.583333333333333</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.083333333333332</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2811</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4488</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.333333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6465</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.625</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9450</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9.799999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.799999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9998</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10.11111111111111</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.111111111111111</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4692</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.111111111111111</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.111111111111111</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9993</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9994</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2412</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13.125</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13.125</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2521</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4043</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.899999999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.899999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6343</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9992</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2990</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3636</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.916666666666667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5468</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.91666666666666</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>16.91666666666666</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6696</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7.777777777777779</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8.666666666666668</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9997</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2557</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6443</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9567</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9995</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Shallow Climb Attempt Average</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>deep_atempt Average</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Played Defense Average</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Robot Died Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2811</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4488</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6465</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9450</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9998</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4692</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9993</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9994</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2412</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2521</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4043</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6343</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9992</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2990</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3636</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5468</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6696</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9997</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2557</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6443</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9567</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9995</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,52 +2325,82 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Algae in Processor (auto) Average</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Algae in Processor (auto) Std</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Algea in Net (auto) Average</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Algea in Net (auto) Std</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Coral L1 (teleop) Average</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Coral L1 (teleop) Std</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Coral L2 (teleop) Average</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Coral L2 (teleop) Std</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Coral L3 (teleop) Average</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Coral L3 (teleop) Std</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Coral L4 (teleop) Average</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Coral L4 (teleop) Std</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
-          <t>Deep Climb Attempt Average</t>
+          <t>Algae in Processor (teleop) Average</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
-          <t>Deep Climb Attempt Std</t>
+          <t>Algae in Processor (teleop) Std</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Algea in Net (teleop) Average</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Algea in Net (teleop) Std</t>
         </is>
       </c>
     </row>
@@ -516,7 +2412,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3892494720807615</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -534,37 +2430,55 @@
         <v>1.083333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.7929614610987591</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="K2" t="n">
+      <c r="O2" t="n">
+        <v>0.6685579234215214</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.544785951633312</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.416666666666667</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.928651593652148</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.916666666666667</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.443375672974064</v>
+      </c>
+      <c r="V2" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.416666666666667</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.583333333333333</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.916666666666667</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.083333333333333</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="W2" t="n">
+        <v>1.164500152881315</v>
+      </c>
+      <c r="X2" t="n">
         <v>0.25</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.621581560508061</v>
       </c>
     </row>
     <row r="3">
@@ -593,7 +2507,7 @@
         <v>1.25</v>
       </c>
       <c r="I3" t="n">
-        <v>1.25</v>
+        <v>1.035098339013531</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -602,28 +2516,46 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>0.75</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
+        <v>1.035098339013531</v>
+      </c>
+      <c r="R3" t="n">
         <v>2.75</v>
       </c>
-      <c r="O3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
+        <v>1.164964745021435</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="U3" t="n">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.7440238091428449</v>
+      </c>
+      <c r="X3" t="n">
         <v>0.25</v>
       </c>
-      <c r="R3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.25</v>
+      <c r="Y3" t="n">
+        <v>0.4629100498862757</v>
       </c>
     </row>
     <row r="4">
@@ -652,37 +2584,55 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="K4" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="O4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="P4" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
+        <v>1.013793755049703</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="N4" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
+        <v>0.8819171036881969</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.444444444444444</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.444444444444444</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.2222222222222222</v>
+      <c r="U4" t="n">
+        <v>1.013793755049703</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -711,36 +2661,54 @@
         <v>0.375</v>
       </c>
       <c r="I5" t="n">
+        <v>0.7440238091428449</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0.375</v>
       </c>
-      <c r="J5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
+        <v>0.7440238091428449</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.25</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
+        <v>1.164964745021435</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.642080561796093</v>
+      </c>
+      <c r="T5" t="n">
         <v>0.75</v>
       </c>
-      <c r="N5" t="n">
-        <v>3.125</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
+        <v>1.48804761828569</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -770,37 +2738,55 @@
         <v>1.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>0.699205898780101</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.6</v>
       </c>
-      <c r="K6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
+        <v>1.776388345929897</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.7</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
+        <v>1.567021236472421</v>
+      </c>
+      <c r="R6" t="n">
         <v>2.2</v>
       </c>
-      <c r="O6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
+        <v>2.740640638812595</v>
+      </c>
+      <c r="T6" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.8</v>
+      <c r="U6" t="n">
+        <v>0.6749485577105528</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.6324555320336759</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.162817093001111</v>
       </c>
     </row>
     <row r="7">
@@ -829,37 +2815,55 @@
         <v>1.444444444444444</v>
       </c>
       <c r="I7" t="n">
-        <v>1.555555555555556</v>
+        <v>1.236033081182611</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="O7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P7" t="n">
         <v>2.555555555555555</v>
       </c>
-      <c r="M7" t="n">
-        <v>2.444444444444445</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
+        <v>1.9436506316151</v>
+      </c>
+      <c r="R7" t="n">
         <v>2.555555555555555</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.444444444444445</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
+        <v>1.740051084818425</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.666666666666667</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
+      <c r="U7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.8819171036881969</v>
       </c>
     </row>
     <row r="8">
@@ -870,7 +2874,7 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -888,37 +2892,55 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="K8" t="n">
+      <c r="O8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P8" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="L8" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="Q8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="O8" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
+        <v>0.7264831572567789</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.222222222222222</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.222222222222222</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
+        <v>1.394433377556793</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="W8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S8" t="n">
-        <v>0.3333333333333334</v>
+      <c r="X8" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4409585518440984</v>
       </c>
     </row>
     <row r="9">
@@ -929,7 +2951,7 @@
         <v>0.1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1</v>
+        <v>0.3162277660168379</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -941,43 +2963,61 @@
         <v>0.1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9</v>
+        <v>0.3162277660168379</v>
       </c>
       <c r="H9" t="n">
         <v>2.1</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>0.9944289260117531</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0.1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
+        <v>0.3162277660168379</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.4</v>
       </c>
-      <c r="M9" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
+        <v>0.9660917830792959</v>
+      </c>
+      <c r="R9" t="n">
         <v>2.5</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
+        <v>1.649915822768611</v>
+      </c>
+      <c r="T9" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.9</v>
+      <c r="U9" t="n">
+        <v>2.201009869229224</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1006,7 +3046,7 @@
         <v>0.4444444444444444</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5270462766947299</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1015,27 +3055,45 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="N10" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1092,10 +3150,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.798809270624444</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1106,7 +3182,7 @@
         <v>0.2</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2</v>
+        <v>0.4216370213557839</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1127,34 +3203,52 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>1.3</v>
       </c>
-      <c r="K12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="O12" t="n">
+        <v>2.263232692902394</v>
+      </c>
+      <c r="P12" t="n">
         <v>0.4</v>
       </c>
-      <c r="M12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.699205898780101</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3</v>
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.911950719959998</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.988868236194652</v>
       </c>
     </row>
     <row r="13">
@@ -1183,37 +3277,55 @@
         <v>1.875</v>
       </c>
       <c r="I13" t="n">
-        <v>0.125</v>
+        <v>0.3535533905932738</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1.875</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.125</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="O13" t="n">
+        <v>1.726888200533798</v>
+      </c>
+      <c r="P13" t="n">
         <v>4</v>
       </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="Q13" t="n">
+        <v>1.772810520855837</v>
+      </c>
+      <c r="R13" t="n">
         <v>3.25</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
+        <v>1.281739888923312</v>
+      </c>
+      <c r="T13" t="n">
         <v>3.375</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
+        <v>1.597989808656935</v>
+      </c>
+      <c r="V13" t="n">
         <v>0.75</v>
       </c>
-      <c r="S13" t="n">
+      <c r="W13" t="n">
+        <v>1.035098339013531</v>
+      </c>
+      <c r="X13" t="n">
         <v>0.25</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4629100498862757</v>
       </c>
     </row>
     <row r="14">
@@ -1242,37 +3354,55 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="I14" t="n">
-        <v>2.428571428571429</v>
+        <v>1.133893419027682</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="K14" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="O14" t="n">
+        <v>0.7867957924694432</v>
+      </c>
+      <c r="P14" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="M14" t="n">
+      <c r="Q14" t="n">
+        <v>0.3779644730092273</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.98805959477601</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.428571428571429</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
+      <c r="Y14" t="n">
+        <v>0.3779644730092273</v>
       </c>
     </row>
     <row r="15">
@@ -1301,37 +3431,55 @@
         <v>0.7</v>
       </c>
       <c r="I15" t="n">
+        <v>0.6749485577105528</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.4216370213557839</v>
+      </c>
+      <c r="P15" t="n">
         <v>0.3</v>
       </c>
-      <c r="J15" t="n">
+      <c r="Q15" t="n">
+        <v>0.6749485577105528</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.577621275493231</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.201009869229224</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
         <v>0.2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.5</v>
+      <c r="Y15" t="n">
+        <v>0.6324555320336759</v>
       </c>
     </row>
     <row r="16">
@@ -1363,34 +3511,52 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="K16" t="n">
+      <c r="O16" t="n">
+        <v>0.242535625036333</v>
+      </c>
+      <c r="P16" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="L16" t="n">
-        <v>0.05882352941176471</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.05882352941176471</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="Q16" t="n">
+        <v>0.242535625036333</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.5882352941176471</v>
       </c>
-      <c r="O16" t="n">
-        <v>1.411764705882353</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="S16" t="n">
+        <v>0.8702602720890289</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.529411764705882</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.470588235294118</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.05882352941176471</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.05882352941176471</v>
+      <c r="U16" t="n">
+        <v>1.87475488593921</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1446,10 +3612,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6666666666666667</v>
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1472,7 +3656,7 @@
         <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.5345224838248488</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1481,34 +3665,52 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0.75</v>
       </c>
-      <c r="K18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="O18" t="n">
+        <v>1.752549163769328</v>
+      </c>
+      <c r="P18" t="n">
         <v>1.625</v>
       </c>
-      <c r="M18" t="n">
+      <c r="Q18" t="n">
+        <v>2.065879266282796</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.625</v>
       </c>
-      <c r="N18" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.25</v>
-      </c>
       <c r="S18" t="n">
-        <v>0.75</v>
+        <v>1.922609833384967</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1519,7 +3721,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.492365963917331</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1537,37 +3739,55 @@
         <v>0.75</v>
       </c>
       <c r="I19" t="n">
-        <v>0.75</v>
+        <v>0.753778361444409</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5773502691896257</v>
+      </c>
+      <c r="N19" t="n">
         <v>1.416666666666667</v>
       </c>
-      <c r="K19" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="O19" t="n">
+        <v>1.164500152881315</v>
+      </c>
+      <c r="P19" t="n">
         <v>2.416666666666667</v>
       </c>
-      <c r="M19" t="n">
-        <v>0.5833333333333335</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="Q19" t="n">
+        <v>2.274696116900546</v>
+      </c>
+      <c r="R19" t="n">
         <v>2.666666666666667</v>
       </c>
-      <c r="O19" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="S19" t="n">
+        <v>1.669694219873444</v>
+      </c>
+      <c r="T19" t="n">
         <v>3.583333333333333</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.416666666666667</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.1666666666666667</v>
+      <c r="U19" t="n">
+        <v>2.314316444667973</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.778498944161523</v>
       </c>
     </row>
     <row r="20">
@@ -1596,7 +3816,7 @@
         <v>2.416666666666667</v>
       </c>
       <c r="I20" t="n">
-        <v>2.416666666666667</v>
+        <v>1.164500152881315</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1605,27 +3825,45 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.75</v>
       </c>
-      <c r="M20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="Q20" t="n">
+        <v>1.864744681524183</v>
+      </c>
+      <c r="R20" t="n">
         <v>6</v>
       </c>
-      <c r="O20" t="n">
-        <v>2</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="S20" t="n">
+        <v>1.809068067466582</v>
+      </c>
+      <c r="T20" t="n">
         <v>5.333333333333333</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
+        <v>1.230914909793327</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1655,37 +3893,55 @@
         <v>1.111111111111111</v>
       </c>
       <c r="I21" t="n">
-        <v>1.111111111111111</v>
+        <v>0.6009252125773316</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.4409585518440984</v>
+      </c>
+      <c r="N21" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="K21" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="O21" t="n">
+        <v>0.8819171036881969</v>
+      </c>
+      <c r="P21" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>2</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="Q21" t="n">
+        <v>1.224744871391589</v>
+      </c>
+      <c r="R21" t="n">
         <v>3.444444444444445</v>
       </c>
-      <c r="O21" t="n">
-        <v>1.444444444444445</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="S21" t="n">
+        <v>1.013793755049703</v>
+      </c>
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
+      <c r="U21" t="n">
+        <v>1.870828693386971</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="22">
@@ -1696,7 +3952,7 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1717,22 +3973,22 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>2.333333333333333</v>
       </c>
-      <c r="K22" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -1744,6 +4000,24 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1776,34 +4050,52 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>5.857142857142857</v>
       </c>
-      <c r="K23" t="n">
-        <v>5.857142857142857</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="O23" t="n">
+        <v>5.580578567035603</v>
+      </c>
+      <c r="P23" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.571428571428572</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="Q23" t="n">
+        <v>1.133893419027682</v>
+      </c>
+      <c r="R23" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="O23" t="n">
-        <v>1.714285714285714</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="S23" t="n">
+        <v>0.7559289460184545</v>
+      </c>
+      <c r="T23" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.8571428571428572</v>
+      <c r="U23" t="n">
+        <v>1.732050807568877</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1832,37 +4124,55 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="I24" t="n">
+        <v>0.5345224838248488</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="J24" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="O24" t="n">
+        <v>0.5345224838248488</v>
+      </c>
+      <c r="P24" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="M24" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="Q24" t="n">
+        <v>0.4879500364742666</v>
+      </c>
+      <c r="R24" t="n">
         <v>2.428571428571428</v>
       </c>
-      <c r="O24" t="n">
-        <v>0.5714285714285716</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="S24" t="n">
+        <v>1.272418020560704</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.714285714285714</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2.714285714285714</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.1428571428571429</v>
+      <c r="U24" t="n">
+        <v>2.288688541085317</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1873,7 +4183,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.5163977794943223</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1891,37 +4201,55 @@
         <v>0.5</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.224744871391589</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1.833333333333333</v>
       </c>
-      <c r="K25" t="n">
-        <v>2.166666666666667</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="O25" t="n">
+        <v>2.041241452319315</v>
+      </c>
+      <c r="P25" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="M25" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0.5</v>
-      </c>
       <c r="Q25" t="n">
-        <v>0.5</v>
+        <v>0.408248290463863</v>
       </c>
       <c r="R25" t="n">
         <v>0.1666666666666667</v>
       </c>
       <c r="S25" t="n">
+        <v>0.408248290463863</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.224744871391589</v>
+      </c>
+      <c r="V25" t="n">
         <v>0.1666666666666667</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.408248290463863</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1953,34 +4281,52 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>0.1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
+        <v>0.3162277660168379</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
         <v>0.2</v>
       </c>
-      <c r="O26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.1</v>
-      </c>
       <c r="S26" t="n">
-        <v>0.1</v>
+        <v>0.6324555320336759</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/scoutlist.xlsx
+++ b/scoutlist.xlsx
@@ -7,10 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Teleop List" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Auto List" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="States List" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Score List" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Score List" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="States List" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Piece List" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,708 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Coral L1 (teleop) score</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Coral L2 (teleop) score</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Coral L3 (teleop) score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Coral L4 (teleop) score</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Algae in Processor (teleop) score</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Algea in Net (teleop) score</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>total teleop score score</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1425</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D2" t="n">
-        <v>9.666666666666666</v>
-      </c>
-      <c r="E2" t="n">
-        <v>9.583333333333334</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.33333333333334</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2811</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E3" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>30.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>4488</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1.555555555555556</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.777777777777778</v>
-      </c>
-      <c r="E4" t="n">
-        <v>7.222222222222222</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>11.88888888888889</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>6465</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>20.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>9450</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>36.6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>9998</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7.666666666666666</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10.22222222222222</v>
-      </c>
-      <c r="E7" t="n">
-        <v>13.33333333333333</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5.777777777777778</v>
-      </c>
-      <c r="H7" t="n">
-        <v>38.99999999999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1540</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.777777777777778</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6.111111111111112</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="H8" t="n">
-        <v>10.66666666666667</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>3674</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.199999999999999</v>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>35.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>4692</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="E10" t="n">
-        <v>15</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>17.11111111111111</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9993</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>21</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9994</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6.600000000000001</v>
-      </c>
-      <c r="G12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="H12" t="n">
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2412</v>
-      </c>
-      <c r="B13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="C13" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" t="n">
-        <v>13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.875</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>51.125</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2521</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1.142857142857143</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>7.142857142857143</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="H14" t="n">
-        <v>9.285714285714286</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>4043</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>14</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H15" t="n">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>6343</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0.1176470588235294</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.1764705882352941</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.352941176470588</v>
-      </c>
-      <c r="E16" t="n">
-        <v>12.64705882352941</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>15.29411764705882</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>9992</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2990</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4.875</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>12.875</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>3636</v>
-      </c>
-      <c r="B19" t="n">
-        <v>2.833333333333333</v>
-      </c>
-      <c r="C19" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="D19" t="n">
-        <v>10.66666666666667</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.91666666666667</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5.333333333333333</v>
-      </c>
-      <c r="H19" t="n">
-        <v>44.00000000000001</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>5468</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="D20" t="n">
-        <v>24</v>
-      </c>
-      <c r="E20" t="n">
-        <v>26.66666666666666</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>58.91666666666666</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>6696</v>
-      </c>
-      <c r="B21" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>13.77777777777778</v>
-      </c>
-      <c r="E21" t="n">
-        <v>15</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>8.888888888888889</v>
-      </c>
-      <c r="H21" t="n">
-        <v>41.77777777777777</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>9997</v>
-      </c>
-      <c r="B22" t="n">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4.666666666666667</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2557</v>
-      </c>
-      <c r="B23" t="n">
-        <v>11.71428571428571</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1.285714285714286</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.142857142857143</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>19.14285714285714</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>6443</v>
-      </c>
-      <c r="B24" t="n">
-        <v>1.142857142857143</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="D24" t="n">
-        <v>9.714285714285714</v>
-      </c>
-      <c r="E24" t="n">
-        <v>13.57142857142857</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>25.28571428571428</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>9567</v>
-      </c>
-      <c r="B25" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>8.333333333333332</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>9995</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,7 +451,47 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total auto score score</t>
+          <t>Coral L1 (teleop) score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Coral L2 (teleop) score</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Coral L3 (teleop) score</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Coral L4 (teleop) score</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Algae in Processor (teleop) score</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Algea in Net (teleop) score</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Auto Score score</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Teleop Score score</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Total Score score</t>
         </is>
       </c>
     </row>
@@ -1180,7 +518,31 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.666666666666666</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.583333333333334</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
         <v>8.083333333333332</v>
+      </c>
+      <c r="O2" t="n">
+        <v>27.33333333333334</v>
+      </c>
+      <c r="P2" t="n">
+        <v>35.41666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -1206,7 +568,31 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11</v>
+      </c>
+      <c r="K3" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
         <v>8.75</v>
+      </c>
+      <c r="O3" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="P3" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -1232,7 +618,31 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.222222222222222</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>2.333333333333333</v>
+      </c>
+      <c r="O4" t="n">
+        <v>11.88888888888889</v>
+      </c>
+      <c r="P4" t="n">
+        <v>14.22222222222222</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +668,31 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.625</v>
+      </c>
+      <c r="O5" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="P5" t="n">
+        <v>23.375</v>
       </c>
     </row>
     <row r="6">
@@ -1284,7 +718,31 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="N6" t="n">
         <v>9.799999999999999</v>
+      </c>
+      <c r="O6" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>46.4</v>
       </c>
     </row>
     <row r="7">
@@ -1310,7 +768,31 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>7.666666666666666</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10.22222222222222</v>
+      </c>
+      <c r="K7" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5.777777777777778</v>
+      </c>
+      <c r="N7" t="n">
         <v>10.11111111111111</v>
+      </c>
+      <c r="O7" t="n">
+        <v>38.99999999999999</v>
+      </c>
+      <c r="P7" t="n">
+        <v>49.1111111111111</v>
       </c>
     </row>
     <row r="8">
@@ -1336,7 +818,31 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.111111111111112</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="N8" t="n">
         <v>1.111111111111111</v>
+      </c>
+      <c r="O8" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11.77777777777778</v>
       </c>
     </row>
     <row r="9">
@@ -1362,7 +868,31 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.199999999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>15.6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -1388,7 +918,31 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="K10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.111111111111111</v>
+      </c>
+      <c r="O10" t="n">
+        <v>17.11111111111111</v>
+      </c>
+      <c r="P10" t="n">
+        <v>20.22222222222222</v>
       </c>
     </row>
     <row r="11">
@@ -1416,6 +970,30 @@
       <c r="H11" t="n">
         <v>0</v>
       </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>21</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>21</v>
+      </c>
+      <c r="P11" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1440,7 +1018,31 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="N12" t="n">
         <v>0.6000000000000001</v>
+      </c>
+      <c r="O12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>21.4</v>
       </c>
     </row>
     <row r="13">
@@ -1466,7 +1068,31 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" t="n">
+        <v>16.875</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
         <v>13.125</v>
+      </c>
+      <c r="O13" t="n">
+        <v>51.125</v>
+      </c>
+      <c r="P13" t="n">
+        <v>64.25</v>
       </c>
     </row>
     <row r="14">
@@ -1492,7 +1118,31 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="N14" t="n">
         <v>4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>9.285714285714286</v>
+      </c>
+      <c r="P14" t="n">
+        <v>13.28571428571429</v>
       </c>
     </row>
     <row r="15">
@@ -1518,7 +1168,31 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>14</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N15" t="n">
         <v>4.899999999999999</v>
+      </c>
+      <c r="O15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>23.4</v>
       </c>
     </row>
     <row r="16">
@@ -1544,7 +1218,31 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.352941176470588</v>
+      </c>
+      <c r="K16" t="n">
+        <v>12.64705882352941</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15.29411764705882</v>
+      </c>
+      <c r="P16" t="n">
+        <v>15.29411764705882</v>
       </c>
     </row>
     <row r="17">
@@ -1572,6 +1270,30 @@
       <c r="H17" t="n">
         <v>0</v>
       </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1596,7 +1318,31 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>12.875</v>
+      </c>
+      <c r="P18" t="n">
+        <v>15.875</v>
       </c>
     </row>
     <row r="19">
@@ -1622,7 +1368,31 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="H19" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="J19" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17.91666666666667</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="N19" t="n">
         <v>6.916666666666667</v>
+      </c>
+      <c r="O19" t="n">
+        <v>44.00000000000001</v>
+      </c>
+      <c r="P19" t="n">
+        <v>50.91666666666667</v>
       </c>
     </row>
     <row r="20">
@@ -1648,7 +1418,31 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J20" t="n">
+        <v>24</v>
+      </c>
+      <c r="K20" t="n">
+        <v>26.66666666666666</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>16.91666666666666</v>
+      </c>
+      <c r="O20" t="n">
+        <v>58.91666666666666</v>
+      </c>
+      <c r="P20" t="n">
+        <v>75.83333333333333</v>
       </c>
     </row>
     <row r="21">
@@ -1674,7 +1468,31 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="H21" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>13.77777777777778</v>
+      </c>
+      <c r="K21" t="n">
+        <v>15</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8.888888888888889</v>
+      </c>
+      <c r="N21" t="n">
         <v>8.666666666666668</v>
+      </c>
+      <c r="O21" t="n">
+        <v>41.77777777777777</v>
+      </c>
+      <c r="P21" t="n">
+        <v>50.44444444444444</v>
       </c>
     </row>
     <row r="22">
@@ -1700,7 +1518,31 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0.3333333333333333</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1726,7 +1568,31 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>11.71428571428571</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>19.14285714285714</v>
+      </c>
+      <c r="P23" t="n">
+        <v>19.14285714285714</v>
       </c>
     </row>
     <row r="24">
@@ -1752,7 +1618,31 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="J24" t="n">
+        <v>9.714285714285714</v>
+      </c>
+      <c r="K24" t="n">
+        <v>13.57142857142857</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>25.28571428571428</v>
+      </c>
+      <c r="P24" t="n">
+        <v>29.28571428571428</v>
       </c>
     </row>
     <row r="25">
@@ -1778,7 +1668,31 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>5.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="P25" t="n">
+        <v>13.83333333333333</v>
       </c>
     </row>
     <row r="26">
@@ -1804,7 +1718,31 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1812,7 +1750,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2273,7 +2211,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/scoutlist.xlsx
+++ b/scoutlist.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scout List" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rankings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,16 +449,16 @@
         <v>10991</v>
       </c>
       <c r="B2" t="n">
-        <v>157.1428571428571</v>
+        <v>170</v>
       </c>
       <c r="C2" t="n">
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>7.142857142857142</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>14.28571428571428</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -468,16 +469,16 @@
         <v>2521</v>
       </c>
       <c r="B3" t="n">
-        <v>183.3333333333333</v>
+        <v>190</v>
       </c>
       <c r="C3" t="n">
-        <v>166.6666666666667</v>
+        <v>150</v>
       </c>
       <c r="D3" t="n">
-        <v>41.66666666666667</v>
+        <v>30</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -494,10 +495,10 @@
         <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>41.66666666666667</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="E4" t="n">
-        <v>16.66666666666666</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -508,7 +509,7 @@
         <v>6845</v>
       </c>
       <c r="B5" t="n">
-        <v>61.53846153846154</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -517,10 +518,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>69.23076923076923</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="F5" t="n">
-        <v>38.46153846153847</v>
+        <v>27.77777777777778</v>
       </c>
     </row>
     <row r="6">
@@ -534,10 +535,10 @@
         <v>200</v>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="E6" t="n">
-        <v>8.333333333333332</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -554,13 +555,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>8.333333333333332</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="E7" t="n">
-        <v>58.33333333333334</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>33.33333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +569,16 @@
         <v>1540</v>
       </c>
       <c r="B8" t="n">
-        <v>185.7142857142857</v>
+        <v>188.8888888888889</v>
       </c>
       <c r="C8" t="n">
-        <v>185.7142857142857</v>
+        <v>188.8888888888889</v>
       </c>
       <c r="D8" t="n">
-        <v>92.85714285714286</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="E8" t="n">
-        <v>35.71428571428572</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -588,19 +589,19 @@
         <v>2733</v>
       </c>
       <c r="B9" t="n">
-        <v>30.76923076923077</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>15.38461538461539</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>46.15384615384615</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F9" t="n">
-        <v>23.07692307692308</v>
+        <v>22.22222222222222</v>
       </c>
     </row>
     <row r="10">
@@ -611,13 +612,13 @@
         <v>200</v>
       </c>
       <c r="C10" t="n">
-        <v>171.4285714285714</v>
+        <v>163.6363636363637</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="E10" t="n">
-        <v>14.28571428571428</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -628,19 +629,19 @@
         <v>753</v>
       </c>
       <c r="B11" t="n">
-        <v>200</v>
+        <v>172.2222222222222</v>
       </c>
       <c r="C11" t="n">
-        <v>181.8181818181818</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>63.63636363636363</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
-        <v>9.090909090909092</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5.555555555555555</v>
       </c>
     </row>
     <row r="12">
@@ -654,13 +655,13 @@
         <v>200</v>
       </c>
       <c r="D12" t="n">
-        <v>45.45454545454545</v>
+        <v>40</v>
       </c>
       <c r="E12" t="n">
-        <v>63.63636363636363</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -668,16 +669,16 @@
         <v>2811</v>
       </c>
       <c r="B13" t="n">
-        <v>138.4615384615385</v>
+        <v>145</v>
       </c>
       <c r="C13" t="n">
-        <v>123.0769230769231</v>
+        <v>130</v>
       </c>
       <c r="D13" t="n">
-        <v>7.692307692307693</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>38.46153846153847</v>
+        <v>40</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -691,16 +692,16 @@
         <v>200</v>
       </c>
       <c r="C14" t="n">
-        <v>163.6363636363637</v>
+        <v>169.2307692307692</v>
       </c>
       <c r="D14" t="n">
-        <v>36.36363636363637</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="E14" t="n">
-        <v>27.27272727272727</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="F14" t="n">
-        <v>9.090909090909092</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="15">
@@ -708,16 +709,16 @@
         <v>5920</v>
       </c>
       <c r="B15" t="n">
-        <v>83.33333333333334</v>
+        <v>87.5</v>
       </c>
       <c r="C15" t="n">
-        <v>83.33333333333334</v>
+        <v>87.5</v>
       </c>
       <c r="D15" t="n">
-        <v>16.66666666666666</v>
+        <v>18.75</v>
       </c>
       <c r="E15" t="n">
-        <v>8.333333333333332</v>
+        <v>12.5</v>
       </c>
       <c r="F15" t="n">
         <v>25</v>
@@ -731,16 +732,16 @@
         <v>200</v>
       </c>
       <c r="C16" t="n">
-        <v>166.6666666666667</v>
+        <v>162.5</v>
       </c>
       <c r="D16" t="n">
-        <v>66.66666666666666</v>
+        <v>62.5</v>
       </c>
       <c r="E16" t="n">
-        <v>66.66666666666666</v>
+        <v>68.75</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="17">
@@ -748,19 +749,19 @@
         <v>4692</v>
       </c>
       <c r="B17" t="n">
-        <v>85.71428571428571</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="C17" t="n">
-        <v>57.14285714285714</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="D17" t="n">
-        <v>7.142857142857142</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>35.71428571428572</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>11.76470588235294</v>
       </c>
     </row>
     <row r="18">
@@ -768,19 +769,19 @@
         <v>6343</v>
       </c>
       <c r="B18" t="n">
-        <v>152.9411764705882</v>
+        <v>140</v>
       </c>
       <c r="C18" t="n">
-        <v>129.4117647058823</v>
+        <v>113.3333333333333</v>
       </c>
       <c r="D18" t="n">
-        <v>29.41176470588236</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="E18" t="n">
-        <v>35.29411764705883</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="F18" t="n">
-        <v>11.76470588235294</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="19">
@@ -788,19 +789,19 @@
         <v>6465</v>
       </c>
       <c r="B19" t="n">
-        <v>100</v>
+        <v>106.6666666666667</v>
       </c>
       <c r="C19" t="n">
-        <v>83.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>33.33333333333333</v>
+        <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>16.66666666666666</v>
+        <v>13.33333333333333</v>
       </c>
     </row>
     <row r="20">
@@ -808,19 +809,19 @@
         <v>749</v>
       </c>
       <c r="B20" t="n">
-        <v>166.6666666666667</v>
+        <v>171.4285714285714</v>
       </c>
       <c r="C20" t="n">
-        <v>133.3333333333333</v>
+        <v>142.8571428571429</v>
       </c>
       <c r="D20" t="n">
-        <v>16.66666666666666</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="E20" t="n">
-        <v>33.33333333333333</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F20" t="n">
-        <v>5.555555555555555</v>
+        <v>9.523809523809524</v>
       </c>
     </row>
     <row r="21">
@@ -828,19 +829,19 @@
         <v>8532</v>
       </c>
       <c r="B21" t="n">
-        <v>184.6153846153846</v>
+        <v>190</v>
       </c>
       <c r="C21" t="n">
-        <v>138.4615384615385</v>
+        <v>140</v>
       </c>
       <c r="D21" t="n">
-        <v>15.38461538461539</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>7.692307692307693</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
-        <v>15.38461538461539</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -848,16 +849,16 @@
         <v>3024</v>
       </c>
       <c r="B22" t="n">
-        <v>181.8181818181818</v>
+        <v>155.5555555555556</v>
       </c>
       <c r="C22" t="n">
-        <v>72.72727272727273</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>27.27272727272727</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -877,7 +878,7 @@
         <v>100</v>
       </c>
       <c r="E23" t="n">
-        <v>12.5</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -888,16 +889,16 @@
         <v>6443</v>
       </c>
       <c r="B24" t="n">
-        <v>183.3333333333333</v>
+        <v>178.9473684210526</v>
       </c>
       <c r="C24" t="n">
-        <v>83.33333333333334</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="D24" t="n">
-        <v>8.333333333333332</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="E24" t="n">
-        <v>58.33333333333334</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -914,10 +915,10 @@
         <v>200</v>
       </c>
       <c r="D25" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E25" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -928,16 +929,16 @@
         <v>847</v>
       </c>
       <c r="B26" t="n">
-        <v>157.1428571428571</v>
+        <v>168.4210526315789</v>
       </c>
       <c r="C26" t="n">
-        <v>157.1428571428571</v>
+        <v>157.8947368421053</v>
       </c>
       <c r="D26" t="n">
-        <v>21.42857142857143</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="E26" t="n">
-        <v>28.57142857142857</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -948,16 +949,16 @@
         <v>955</v>
       </c>
       <c r="B27" t="n">
-        <v>185.7142857142857</v>
+        <v>189.4736842105263</v>
       </c>
       <c r="C27" t="n">
-        <v>185.7142857142857</v>
+        <v>189.4736842105263</v>
       </c>
       <c r="D27" t="n">
-        <v>71.42857142857143</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="E27" t="n">
-        <v>35.71428571428572</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -968,19 +969,19 @@
         <v>3712</v>
       </c>
       <c r="B28" t="n">
-        <v>80</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="C28" t="n">
-        <v>26.66666666666667</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>26.66666666666667</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>16.66666666666666</v>
       </c>
     </row>
     <row r="29">
@@ -988,19 +989,19 @@
         <v>5468</v>
       </c>
       <c r="B29" t="n">
-        <v>200</v>
+        <v>189.4736842105263</v>
       </c>
       <c r="C29" t="n">
-        <v>184.6153846153846</v>
+        <v>189.4736842105263</v>
       </c>
       <c r="D29" t="n">
-        <v>84.61538461538461</v>
+        <v>89.47368421052632</v>
       </c>
       <c r="E29" t="n">
-        <v>23.07692307692308</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="F29" t="n">
-        <v>7.692307692307693</v>
+        <v>10.52631578947368</v>
       </c>
     </row>
     <row r="30">
@@ -1011,16 +1012,16 @@
         <v>200</v>
       </c>
       <c r="C30" t="n">
-        <v>200</v>
+        <v>186.6666666666667</v>
       </c>
       <c r="D30" t="n">
-        <v>36.36363636363637</v>
+        <v>40</v>
       </c>
       <c r="E30" t="n">
-        <v>36.36363636363637</v>
+        <v>40</v>
       </c>
       <c r="F30" t="n">
-        <v>9.090909090909092</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="31">
@@ -1028,16 +1029,16 @@
         <v>4043</v>
       </c>
       <c r="B31" t="n">
-        <v>200</v>
+        <v>190.9090909090909</v>
       </c>
       <c r="C31" t="n">
-        <v>200</v>
+        <v>190.9090909090909</v>
       </c>
       <c r="D31" t="n">
-        <v>33.33333333333333</v>
+        <v>22.72727272727273</v>
       </c>
       <c r="E31" t="n">
-        <v>20</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1048,19 +1049,19 @@
         <v>1359</v>
       </c>
       <c r="B32" t="n">
-        <v>200</v>
+        <v>187.5</v>
       </c>
       <c r="C32" t="n">
-        <v>133.3333333333333</v>
+        <v>125</v>
       </c>
       <c r="D32" t="n">
-        <v>16.66666666666666</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="n">
-        <v>8.333333333333332</v>
+        <v>18.75</v>
       </c>
       <c r="F32" t="n">
-        <v>8.333333333333332</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="33">
@@ -1068,19 +1069,19 @@
         <v>9567</v>
       </c>
       <c r="B33" t="n">
-        <v>176.4705882352941</v>
+        <v>182.6086956521739</v>
       </c>
       <c r="C33" t="n">
-        <v>58.82352941176471</v>
+        <v>69.56521739130434</v>
       </c>
       <c r="D33" t="n">
-        <v>5.88235294117647</v>
+        <v>8.695652173913043</v>
       </c>
       <c r="E33" t="n">
-        <v>11.76470588235294</v>
+        <v>17.39130434782609</v>
       </c>
       <c r="F33" t="n">
-        <v>5.88235294117647</v>
+        <v>4.347826086956522</v>
       </c>
     </row>
     <row r="34">
@@ -1091,13 +1092,13 @@
         <v>200</v>
       </c>
       <c r="C34" t="n">
-        <v>200</v>
+        <v>189.4736842105263</v>
       </c>
       <c r="D34" t="n">
-        <v>46.15384615384615</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="E34" t="n">
-        <v>23.07692307692308</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1117,7 +1118,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1128,19 +1129,430 @@
         <v>3673</v>
       </c>
       <c r="B36" t="n">
-        <v>22.22222222222222</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F36" t="n">
-        <v>22.22222222222222</v>
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Before dead bot  rank score</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>After dead bot  rank score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>10991</v>
+      </c>
+      <c r="B2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2521</v>
+      </c>
+      <c r="B3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4125</v>
+      </c>
+      <c r="B4" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6845</v>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-5.111111111111111</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7034</v>
+      </c>
+      <c r="B6" t="n">
+        <v>14.8235294117647</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14.8235294117647</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9438</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-8.333333333333332</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B8" t="n">
+        <v>18.66666666666666</v>
+      </c>
+      <c r="C8" t="n">
+        <v>18.66666666666666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2733</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4.444444444444445</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-4.444444444444445</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4060</v>
+      </c>
+      <c r="B10" t="n">
+        <v>12.18181818181818</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12.18181818181818</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>753</v>
+      </c>
+      <c r="B11" t="n">
+        <v>13.77777777777778</v>
+      </c>
+      <c r="C11" t="n">
+        <v>11.55555555555555</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9430</v>
+      </c>
+      <c r="B12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12.66666666666667</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2811</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4061</v>
+      </c>
+      <c r="B14" t="n">
+        <v>14.46153846153846</v>
+      </c>
+      <c r="C14" t="n">
+        <v>11.38461538461539</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5920</v>
+      </c>
+      <c r="B15" t="n">
+        <v>7.125</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-2.875</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>997</v>
+      </c>
+      <c r="B16" t="n">
+        <v>18.375</v>
+      </c>
+      <c r="C16" t="n">
+        <v>15.875</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4692</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4.588235294117647</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.1176470588235299</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6343</v>
+      </c>
+      <c r="B18" t="n">
+        <v>10.93333333333333</v>
+      </c>
+      <c r="C18" t="n">
+        <v>8.266666666666667</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6465</v>
+      </c>
+      <c r="B19" t="n">
+        <v>7.733333333333333</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>749</v>
+      </c>
+      <c r="B20" t="n">
+        <v>12.57142857142857</v>
+      </c>
+      <c r="C20" t="n">
+        <v>8.761904761904763</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8532</v>
+      </c>
+      <c r="B21" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3024</v>
+      </c>
+      <c r="B22" t="n">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7.333333333333334</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B23" t="n">
+        <v>19.84615384615385</v>
+      </c>
+      <c r="C23" t="n">
+        <v>19.84615384615385</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6443</v>
+      </c>
+      <c r="B24" t="n">
+        <v>10.84210526315789</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10.84210526315789</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>846</v>
+      </c>
+      <c r="B25" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>847</v>
+      </c>
+      <c r="B26" t="n">
+        <v>13.78947368421053</v>
+      </c>
+      <c r="C26" t="n">
+        <v>13.78947368421053</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>955</v>
+      </c>
+      <c r="B27" t="n">
+        <v>18.31578947368421</v>
+      </c>
+      <c r="C27" t="n">
+        <v>18.31578947368421</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3712</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4.555555555555555</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-2.111111111111111</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>5468</v>
+      </c>
+      <c r="B29" t="n">
+        <v>18</v>
+      </c>
+      <c r="C29" t="n">
+        <v>13.78947368421053</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2374</v>
+      </c>
+      <c r="B30" t="n">
+        <v>16.26666666666667</v>
+      </c>
+      <c r="C30" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>4043</v>
+      </c>
+      <c r="B31" t="n">
+        <v>14.45454545454546</v>
+      </c>
+      <c r="C31" t="n">
+        <v>14.45454545454546</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1359</v>
+      </c>
+      <c r="B32" t="n">
+        <v>10.625</v>
+      </c>
+      <c r="C32" t="n">
+        <v>8.125</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>9567</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>6.260869565217392</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2926</v>
+      </c>
+      <c r="B34" t="n">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>9023</v>
+      </c>
+      <c r="B35" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="C35" t="n">
+        <v>16.66666666666667</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3673</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-6.666666666666667</v>
       </c>
     </row>
   </sheetData>
